--- a/healthcare_surveys/008_laser_treatment_side_effects_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/008_laser_treatment_side_effects_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Which of the following are you experiencing?</t>
+          <t>Which of the following treatments have you had?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,14 +594,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How often do you feel these symptoms?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Choose one of the following</t>
-        </is>
-      </c>
+          <t>How many of these treatments have you had?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -611,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How severe are these symptoms?</t>
+          <t>Which of the following symptoms are you experiencing?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -644,10 +640,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How long have you had these symptoms?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How often do you feel these symptoms?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Choose one of the following</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -657,7 +657,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -667,14 +667,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What time of day do you experience these symptoms?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Choose a time</t>
-        </is>
-      </c>
+          <t>How severe are these symptoms?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -684,7 +680,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -694,14 +690,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Do you experience these symptoms at a specific time of year?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Check a box</t>
-        </is>
-      </c>
+          <t>How long have you had these symptoms?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -711,7 +703,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -721,7 +713,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What treatments do you have had?</t>
+          <t>What time of day do you experience these symptoms?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -734,7 +726,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -744,10 +736,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How many treatments have you had?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you experience these symptoms at a specific time of year?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Check a box</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -757,7 +753,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -767,14 +763,10 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Have you had other treatments?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
+          <t>How long do you experience these symptoms?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -794,7 +786,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Have you noticed any other side effects?</t>
+          <t>Have you had other treatments?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -821,7 +813,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Do you have any other health issues?</t>
+          <t>Have you noticed any other side effects?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -838,7 +830,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -848,10 +840,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>How long have you had these symptoms?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Do you have any other health issues?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Check all that apply</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -871,7 +867,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How long will these symptoms persist?</t>
+          <t>Question 14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -884,7 +880,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -894,14 +890,10 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Do you have any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
+          <t>How long will these symptoms persist?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -921,7 +913,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Do you experience any other symptoms?</t>
+          <t>Have you experienced any other symptoms?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -938,7 +930,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -948,227 +940,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How long will these symptoms persist?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Do you experience any other symptoms?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Check all that apply</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>question_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Have you experienced any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>question_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>question_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>question_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>question_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>question_25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Do you experience any other symptoms?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Check all that apply</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1185,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1218,12 +998,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>redness</t>
+          <t>laser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Redness</t>
+          <t>Laser</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>blisters</t>
+          <t>chemical_peeling</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Blisters</t>
+          <t>Chemical peeling</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1032,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>itching</t>
+          <t>microdermabrasion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Itching</t>
+          <t>Microdermabrasion</t>
         </is>
       </c>
     </row>
@@ -1269,335 +1049,335 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>burning</t>
+          <t>micro-needling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Burning</t>
+          <t>Micro-needling</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>swelling</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Swelling</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>blisters</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Blisters</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sometimes</t>
+          <t>itching</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sometimes</t>
+          <t>Itching</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>burning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Burning</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>usually</t>
+          <t>swelling</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Usually</t>
+          <t>Swelling</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1_-_very_mild</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1 - Very mild</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2_-_mild</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2 - Mild</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3_-_moderate</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3 - Moderate</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4_-_severe</t>
+          <t>usually</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4 - Severe</t>
+          <t>Usually</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5_-_very_severe</t>
+          <t>1_-_very_mild</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5 - Very severe</t>
+          <t>1 - Very mild</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>only_during_treatment</t>
+          <t>2_-_mild</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Only during treatment</t>
+          <t>2 - Mild</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>only_outside_of_treatment</t>
+          <t>3_-_moderate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Only outside of treatment</t>
+          <t>3 - Moderate</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>all_year_round</t>
+          <t>4_-_severe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>All year round</t>
+          <t>4 - Severe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>5_-_very_severe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>5 - Very severe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>laser</t>
+          <t>only_during_treatment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Laser</t>
+          <t>Only during treatment</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>chemical_peeling</t>
+          <t>only_outside_of_treatment</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chemical peeling</t>
+          <t>Only outside of treatment</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>microdermabrasion</t>
+          <t>all_year_round</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Microdermabrasion</t>
+          <t>All year round</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>micro-needling</t>
+          <t>1-7_days</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Micro-needling</t>
+          <t>1-7 days</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_10_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>8-14_days</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>8-14 days</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1389,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>15-30_days</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>15-30 days</t>
         </is>
       </c>
     </row>
@@ -1626,63 +1406,63 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>chemical_peeling</t>
+          <t>more_than_30_days</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chemical peeling</t>
+          <t>More than 30 days</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>microdermabrasion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Microdermabrasion</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>micro-needling</t>
+          <t>chemical_peeling</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Micro-needling</t>
+          <t>Chemical peeling</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_10_choices</t>
+          <t>question_11_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>microdermabrasion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Microdermabrasion</t>
         </is>
       </c>
     </row>
@@ -1694,12 +1474,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>micro-needling</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Micro-needling</t>
         </is>
       </c>
     </row>
@@ -1711,97 +1491,97 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>redness</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Redness</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>blisters</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Blisters</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>itching</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Itching</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>burning</t>
+          <t>blisters</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Burning</t>
+          <t>Blisters</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>swelling</t>
+          <t>itching</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Swelling</t>
+          <t>Itching</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_11_choices</t>
+          <t>question_12_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>burning</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Burning</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1593,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>swelling</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Swelling</t>
         </is>
       </c>
     </row>
@@ -1830,80 +1610,80 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>allergies</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Allergies</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>high_blood_pressure</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>High blood pressure</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>question_12_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>high_blood_pressure</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>High blood pressure</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_13_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>redness</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redness</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1915,12 +1695,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>blisters</t>
+          <t>1-7_days</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Blisters</t>
+          <t>1-7 days</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1712,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>itching</t>
+          <t>8-14_days</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Itching</t>
+          <t>8-14 days</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1729,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>burning</t>
+          <t>15-30_days</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Burning</t>
+          <t>15-30 days</t>
         </is>
       </c>
     </row>
@@ -1966,29 +1746,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>swelling</t>
+          <t>more_than_30_days</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Swelling</t>
+          <t>More than 30 days</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>question_15_choices</t>
+          <t>question_16_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2000,12 +1780,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -2017,12 +1797,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>redness</t>
+          <t>blisters</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redness</t>
+          <t>Blisters</t>
         </is>
       </c>
     </row>
@@ -2034,12 +1814,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>blisters</t>
+          <t>itching</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Blisters</t>
+          <t>Itching</t>
         </is>
       </c>
     </row>
@@ -2051,12 +1831,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>itching</t>
+          <t>burning</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Itching</t>
+          <t>Burning</t>
         </is>
       </c>
     </row>
@@ -2068,12 +1848,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>burning</t>
+          <t>swelling</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Burning</t>
+          <t>Swelling</t>
         </is>
       </c>
     </row>
@@ -2085,29 +1865,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>swelling</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Swelling</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>question_16_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2119,12 +1899,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1-7_days</t>
+          <t>redness</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1-7 days</t>
+          <t>Redness</t>
         </is>
       </c>
     </row>
@@ -2136,12 +1916,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8-14_days</t>
+          <t>blisters</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>8-14 days</t>
+          <t>Blisters</t>
         </is>
       </c>
     </row>
@@ -2153,12 +1933,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15-30_days</t>
+          <t>itching</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>15-30 days</t>
+          <t>Itching</t>
         </is>
       </c>
     </row>
@@ -2170,962 +1950,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>more_than_30_days</t>
+          <t>burning</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>More than 30 days</t>
+          <t>Burning</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>swelling</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Swelling</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>question_18_choices</t>
+          <t>question_17_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>redness</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>question_18_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>question_19_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>question_20_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>question_21_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>question_22_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>question_23_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>question_24_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>redness</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Redness</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>blisters</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Blisters</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>itching</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Itching</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>burning</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>swelling</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Swelling</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>question_25_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
